--- a/output_data/charts/0500000US39141.xlsx
+++ b/output_data/charts/0500000US39141.xlsx
@@ -161,10 +161,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>2012</c:v>
                 </c:pt>
@@ -200,51 +200,57 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:f>Sheet1!$B$2:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>1.04284995996201</c:v>
+                  <c:v>0.9683606771075811</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.266665433902254</c:v>
+                  <c:v>1.017030640359474</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.050185379006936</c:v>
+                  <c:v>1.024888683897749</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.967624415727248</c:v>
+                  <c:v>1.838740720373935</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.201711613095831</c:v>
+                  <c:v>2.189272564434272</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.038767956840851</c:v>
+                  <c:v>2.093657863371181</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.252076437894211</c:v>
+                  <c:v>2.255979516642728</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.231910366479682</c:v>
+                  <c:v>2.157513354263693</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.373315305726162</c:v>
+                  <c:v>2.47320692497939</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.651762969974527</c:v>
+                  <c:v>2.644802962179317</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.639323277511646</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.778136710169273</c:v>
+                  <c:v>2.683809277684456</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.670669656852106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -284,7 +290,7 @@
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="4"/>
+          <c:max val="3"/>
           <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
@@ -314,14 +320,8 @@
             <a:gs pos="0">
               <a:srgbClr val="80C080"/>
             </a:gs>
-            <a:gs pos="75000">
+            <a:gs pos="100000">
               <a:srgbClr val="80C080"/>
-            </a:gs>
-            <a:gs pos="75000">
-              <a:srgbClr val="FFFF80"/>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:srgbClr val="FFFF80"/>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
@@ -658,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -677,7 +677,7 @@
         <v>2012</v>
       </c>
       <c r="B2" s="1">
-        <v>1.04284995996201</v>
+        <v>0.9683606771075811</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -685,7 +685,7 @@
         <v>2013</v>
       </c>
       <c r="B3" s="1">
-        <v>1.266665433902254</v>
+        <v>1.017030640359474</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -693,7 +693,7 @@
         <v>2014</v>
       </c>
       <c r="B4" s="1">
-        <v>1.050185379006936</v>
+        <v>1.024888683897749</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -701,7 +701,7 @@
         <v>2015</v>
       </c>
       <c r="B5" s="1">
-        <v>1.967624415727248</v>
+        <v>1.838740720373935</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -709,7 +709,7 @@
         <v>2016</v>
       </c>
       <c r="B6" s="1">
-        <v>2.201711613095831</v>
+        <v>2.189272564434272</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -717,7 +717,7 @@
         <v>2017</v>
       </c>
       <c r="B7" s="1">
-        <v>2.038767956840851</v>
+        <v>2.093657863371181</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -725,7 +725,7 @@
         <v>2018</v>
       </c>
       <c r="B8" s="1">
-        <v>2.252076437894211</v>
+        <v>2.255979516642728</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -733,7 +733,7 @@
         <v>2019</v>
       </c>
       <c r="B9" s="1">
-        <v>2.231910366479682</v>
+        <v>2.157513354263693</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -741,7 +741,7 @@
         <v>2020</v>
       </c>
       <c r="B10" s="1">
-        <v>2.373315305726162</v>
+        <v>2.47320692497939</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -749,7 +749,7 @@
         <v>2021</v>
       </c>
       <c r="B11" s="1">
-        <v>2.651762969974527</v>
+        <v>2.644802962179317</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -765,7 +765,15 @@
         <v>2023</v>
       </c>
       <c r="B13" s="1">
-        <v>2.778136710169273</v>
+        <v>2.683809277684456</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2.670669656852106</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39141.xlsx
+++ b/output_data/charts/0500000US39141.xlsx
@@ -161,47 +161,32 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
+              <c:f>Sheet1!$A$2:$A$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2012</c:v>
+                  <c:v>2017</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2013</c:v>
+                  <c:v>2018</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2014</c:v>
+                  <c:v>2019</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2015</c:v>
+                  <c:v>2020</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2016</c:v>
+                  <c:v>2021</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2017</c:v>
+                  <c:v>2022</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2018</c:v>
+                  <c:v>2023</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="12">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -209,48 +194,33 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$14</c:f>
+              <c:f>Sheet1!$B$2:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.9683606771075811</c:v>
+                  <c:v>2.093657863371181</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.017030640359474</c:v>
+                  <c:v>2.255979516642728</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.024888683897749</c:v>
+                  <c:v>2.134450280476736</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.838740720373935</c:v>
+                  <c:v>2.47320692497939</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.189272564434272</c:v>
+                  <c:v>2.644802962179317</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.093657863371181</c:v>
+                  <c:v>2.639323277511646</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.255979516642728</c:v>
+                  <c:v>2.707068096653314</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.157513354263693</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.47320692497939</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2.644802962179317</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.639323277511646</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2.683809277684456</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.670669656852106</c:v>
+                  <c:v>2.676698256528974</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -658,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -674,106 +644,66 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="B2" s="1">
-        <v>0.9683606771075811</v>
+        <v>2.093657863371181</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="B3" s="1">
-        <v>1.017030640359474</v>
+        <v>2.255979516642728</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="B4" s="1">
-        <v>1.024888683897749</v>
+        <v>2.134450280476736</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="B5" s="1">
-        <v>1.838740720373935</v>
+        <v>2.47320692497939</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B6" s="1">
-        <v>2.189272564434272</v>
+        <v>2.644802962179317</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="B7" s="1">
-        <v>2.093657863371181</v>
+        <v>2.639323277511646</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B8" s="1">
-        <v>2.255979516642728</v>
+        <v>2.707068096653314</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="B9" s="1">
-        <v>2.157513354263693</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B10" s="1">
-        <v>2.47320692497939</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B11" s="1">
-        <v>2.644802962179317</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2.639323277511646</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2.683809277684456</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2.670669656852106</v>
+        <v>2.676698256528974</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39141.xlsx
+++ b/output_data/charts/0500000US39141.xlsx
@@ -161,32 +161,41 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$9</c:f>
+              <c:f>Sheet1!$A$2:$A$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>2023</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
@@ -194,32 +203,41 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$9</c:f>
+              <c:f>Sheet1!$B$2:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
+                  <c:v>1.196537226588139</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.838740720373935</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.172687166218861</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>2.093657863371181</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>2.255979516642728</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>2.134450280476736</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>2.47320692497939</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>2.644802962179317</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>2.639323277511646</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>2.707068096653314</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>2.676698256528974</c:v>
                 </c:pt>
               </c:numCache>
@@ -628,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -644,65 +662,89 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B2" s="1">
-        <v>2.093657863371181</v>
+        <v>1.196537226588139</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B3" s="1">
-        <v>2.255979516642728</v>
+        <v>1.838740720373935</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B4" s="1">
-        <v>2.134450280476736</v>
+        <v>2.172687166218861</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B5" s="1">
-        <v>2.47320692497939</v>
+        <v>2.093657863371181</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B6" s="1">
-        <v>2.644802962179317</v>
+        <v>2.255979516642728</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B7" s="1">
-        <v>2.639323277511646</v>
+        <v>2.134450280476736</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B8" s="1">
-        <v>2.707068096653314</v>
+        <v>2.47320692497939</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2.644802962179317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2.639323277511646</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2.707068096653314</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2">
         <v>2024</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B12" s="1">
         <v>2.676698256528974</v>
       </c>
     </row>
